--- a/Unity/Assets/Config/Excel/ActivityConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ActivityConfig.xlsx
@@ -1,38 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B340FE3D-0D92-4271-8D7E-C74BB3A7C1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -141,15 +134,15 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="Item_Template" type="4" background="1" refreshedVersion="2" saveData="1">
-    <webPr parsePre="1" consecutive="1" xl2000="1" sourceData="1" xml="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlFormat="all" htmlTables="1"/>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="Item_Template" type="4" refreshedVersion="2" background="1" saveData="1">
+    <webPr xml="1" sourceData="1" parsePre="1" consecutive="1" xl2000="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlTables="1" htmlFormat="all"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="234">
   <si>
     <t>Id</t>
   </si>
@@ -848,18 +841,28 @@
   <si>
     <t>1;1000000@1000018;40@1000019;200@3;3000@1010015;1</t>
   </si>
+  <si>
+    <t>1;500000@1000018;30@1023008;3@1000022;5@1010002;1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;500000@1000018;30@1024008;3@1000022;5@1010002;1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000022;5@1;500000@1000018;30@1000014;1@1000020;1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010002;1@1;500000@1000018;30@1000022;5@1022009;2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -894,150 +897,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -1048,7 +907,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1063,8 +922,23 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="49">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1079,271 +953,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149601733451338"/>
+        <fgColor theme="0" tint="-0.14957121494186223"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149632251960814"/>
+        <fgColor theme="0" tint="-0.14960173345133823"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.79958494827112647"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.79958494827112647"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.79958494827112647"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.79958494827112647"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.79958494827112647"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.79958494827112647"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799615466780602"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799615466780602"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799615466780602"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799615466780602"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799615466780602"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799615466780602"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1354,7 +1042,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1451,7 +1139,7 @@
         <color theme="1" tint="0.499984740745262"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.399639881588183"/>
+        <color theme="4" tint="0.39960936307870726"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1470,1166 +1158,939 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="361">
+  <cellStyleXfs count="313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2674,380 +2135,335 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="361">
+  <cellStyles count="313">
+    <cellStyle name="20% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 3 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 4" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 4 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 5" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 6" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 3 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 3 3" xfId="13" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 4" xfId="14" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 4 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 5" xfId="16" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 5 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 6" xfId="18" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 7" xfId="19" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2 3" xfId="23" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 3" xfId="24" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 3 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 4" xfId="26" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 4 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 5" xfId="28" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 6" xfId="29" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 3" xfId="30" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 3 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 3 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 4" xfId="33" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 4 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 5" xfId="35" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 5 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 6" xfId="37" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 7" xfId="38" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2 3" xfId="42" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 3" xfId="43" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 3 2" xfId="44" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 4" xfId="45" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 4 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 5" xfId="47" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 6" xfId="48" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 3" xfId="49" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 3 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 3 3" xfId="51" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 4 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 5" xfId="54" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 5 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 6" xfId="56" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 7" xfId="57" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 2" xfId="58" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="59" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2 2" xfId="60" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2 3" xfId="61" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 3" xfId="62" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 3 2" xfId="63" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 4" xfId="64" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 4 2" xfId="65" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 5" xfId="66" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 6" xfId="67" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 3" xfId="68" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 3 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 3 3" xfId="70" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 4" xfId="71" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 4 2" xfId="72" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 5" xfId="73" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 5 2" xfId="74" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 6" xfId="75" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 7" xfId="76" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 2" xfId="77" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="78" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2 2" xfId="79" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2 3" xfId="80" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 3" xfId="81" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 3 2" xfId="82" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 4" xfId="83" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 4 2" xfId="84" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 5" xfId="85" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 6" xfId="86" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 3" xfId="87" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 3 2" xfId="88" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 3 3" xfId="89" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 4" xfId="90" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 4 2" xfId="91" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 5" xfId="92" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 5 2" xfId="93" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 6" xfId="94" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 7" xfId="95" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 2" xfId="96" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="97" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2 2" xfId="98" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2 3" xfId="99" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 3" xfId="100" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 3 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 4" xfId="102" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 4 2" xfId="103" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 5" xfId="104" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 6" xfId="105" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 3" xfId="106" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 3 2" xfId="107" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 3 3" xfId="108" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 4" xfId="109" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 4 2" xfId="110" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 5" xfId="111" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 5 2" xfId="112" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 6" xfId="113" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 7" xfId="114" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 2" xfId="115" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="116" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2 2" xfId="117" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2 3" xfId="118" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 3" xfId="119" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 3 2" xfId="120" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 4" xfId="121" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 4 2" xfId="122" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 5" xfId="123" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 6" xfId="124" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 3" xfId="125" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 3 2" xfId="126" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 3 3" xfId="127" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 4" xfId="128" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 4 2" xfId="129" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 5" xfId="130" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 5 2" xfId="131" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 6" xfId="132" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 7" xfId="133" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 2" xfId="134" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="135" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2 2" xfId="136" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2 3" xfId="137" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 3" xfId="138" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 3 2" xfId="139" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 4" xfId="140" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 4 2" xfId="141" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 5" xfId="142" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 6" xfId="143" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 3" xfId="144" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 3 2" xfId="145" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 3 3" xfId="146" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 4" xfId="147" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 4 2" xfId="148" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 5" xfId="149" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 5 2" xfId="150" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 6" xfId="151" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 7" xfId="152" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 2" xfId="153" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="154" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2 2" xfId="155" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2 3" xfId="156" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 3" xfId="157" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 3 2" xfId="158" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 4" xfId="159" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 4 2" xfId="160" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 5" xfId="161" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 6" xfId="162" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 3" xfId="163" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 3 2" xfId="164" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 3 3" xfId="165" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 4" xfId="166" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 4 2" xfId="167" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 5" xfId="168" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 5 2" xfId="169" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 6" xfId="170" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 7" xfId="171" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 2" xfId="172" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="173" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2 2" xfId="174" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2 3" xfId="175" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 3" xfId="176" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 3 2" xfId="177" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 4" xfId="178" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 4 2" xfId="179" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 5" xfId="180" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 6" xfId="181" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 3" xfId="182" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 3 2" xfId="183" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 3 3" xfId="184" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 4" xfId="185" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 4 2" xfId="186" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 5" xfId="187" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 5 2" xfId="188" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 6" xfId="189" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 7" xfId="190" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 2" xfId="191" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="192" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2 2" xfId="193" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2 3" xfId="194" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 3" xfId="195" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 3 2" xfId="196" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 4" xfId="197" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 4 2" xfId="198" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 5" xfId="199" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 6" xfId="200" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 3" xfId="201" xr:uid="{00000000-0005-0000-0000-0000F9000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 3 2" xfId="202" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 3 3" xfId="203" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 4" xfId="204" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 4 2" xfId="205" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 5" xfId="206" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 5 2" xfId="207" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 6" xfId="208" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 7" xfId="209" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 2" xfId="210" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="211" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2 2" xfId="212" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2 3" xfId="213" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 3" xfId="214" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 3 2" xfId="215" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 4" xfId="216" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 4 2" xfId="217" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 5" xfId="218" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 6" xfId="219" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 3" xfId="220" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 3 2" xfId="221" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 3 3" xfId="222" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 4" xfId="223" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 4 2" xfId="224" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 5" xfId="225" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 5 2" xfId="226" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 6" xfId="227" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 7" xfId="228" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 1 2" xfId="49"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="50"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2 2" xfId="51"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2 3" xfId="52"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 3" xfId="53"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 3 2" xfId="54"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 4" xfId="55"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 4 2" xfId="56"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 5" xfId="57"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 6" xfId="58"/>
-    <cellStyle name="20% - 强调文字颜色 1 3" xfId="59"/>
-    <cellStyle name="20% - 强调文字颜色 1 3 2" xfId="60"/>
-    <cellStyle name="20% - 强调文字颜色 1 3 3" xfId="61"/>
-    <cellStyle name="20% - 强调文字颜色 1 4" xfId="62"/>
-    <cellStyle name="20% - 强调文字颜色 1 4 2" xfId="63"/>
-    <cellStyle name="20% - 强调文字颜色 1 5" xfId="64"/>
-    <cellStyle name="20% - 强调文字颜色 1 5 2" xfId="65"/>
-    <cellStyle name="20% - 强调文字颜色 1 6" xfId="66"/>
-    <cellStyle name="20% - 强调文字颜色 1 7" xfId="67"/>
-    <cellStyle name="20% - 强调文字颜色 2 2" xfId="68"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="69"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2 2" xfId="70"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2 3" xfId="71"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 3" xfId="72"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 3 2" xfId="73"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 4" xfId="74"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 4 2" xfId="75"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 5" xfId="76"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 6" xfId="77"/>
-    <cellStyle name="20% - 强调文字颜色 2 3" xfId="78"/>
-    <cellStyle name="20% - 强调文字颜色 2 3 2" xfId="79"/>
-    <cellStyle name="20% - 强调文字颜色 2 3 3" xfId="80"/>
-    <cellStyle name="20% - 强调文字颜色 2 4" xfId="81"/>
-    <cellStyle name="20% - 强调文字颜色 2 4 2" xfId="82"/>
-    <cellStyle name="20% - 强调文字颜色 2 5" xfId="83"/>
-    <cellStyle name="20% - 强调文字颜色 2 5 2" xfId="84"/>
-    <cellStyle name="20% - 强调文字颜色 2 6" xfId="85"/>
-    <cellStyle name="20% - 强调文字颜色 2 7" xfId="86"/>
-    <cellStyle name="20% - 强调文字颜色 3 2" xfId="87"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="88"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2 2" xfId="89"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2 3" xfId="90"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 3" xfId="91"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 3 2" xfId="92"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 4" xfId="93"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 4 2" xfId="94"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 5" xfId="95"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 6" xfId="96"/>
-    <cellStyle name="20% - 强调文字颜色 3 3" xfId="97"/>
-    <cellStyle name="20% - 强调文字颜色 3 3 2" xfId="98"/>
-    <cellStyle name="20% - 强调文字颜色 3 3 3" xfId="99"/>
-    <cellStyle name="20% - 强调文字颜色 3 4" xfId="100"/>
-    <cellStyle name="20% - 强调文字颜色 3 4 2" xfId="101"/>
-    <cellStyle name="20% - 强调文字颜色 3 5" xfId="102"/>
-    <cellStyle name="20% - 强调文字颜色 3 5 2" xfId="103"/>
-    <cellStyle name="20% - 强调文字颜色 3 6" xfId="104"/>
-    <cellStyle name="20% - 强调文字颜色 3 7" xfId="105"/>
-    <cellStyle name="20% - 强调文字颜色 4 2" xfId="106"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="107"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2 2" xfId="108"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2 3" xfId="109"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 3" xfId="110"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 3 2" xfId="111"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 4" xfId="112"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 4 2" xfId="113"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 5" xfId="114"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 6" xfId="115"/>
-    <cellStyle name="20% - 强调文字颜色 4 3" xfId="116"/>
-    <cellStyle name="20% - 强调文字颜色 4 3 2" xfId="117"/>
-    <cellStyle name="20% - 强调文字颜色 4 3 3" xfId="118"/>
-    <cellStyle name="20% - 强调文字颜色 4 4" xfId="119"/>
-    <cellStyle name="20% - 强调文字颜色 4 4 2" xfId="120"/>
-    <cellStyle name="20% - 强调文字颜色 4 5" xfId="121"/>
-    <cellStyle name="20% - 强调文字颜色 4 5 2" xfId="122"/>
-    <cellStyle name="20% - 强调文字颜色 4 6" xfId="123"/>
-    <cellStyle name="20% - 强调文字颜色 4 7" xfId="124"/>
-    <cellStyle name="20% - 强调文字颜色 5 2" xfId="125"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="126"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2 2" xfId="127"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2 3" xfId="128"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 3" xfId="129"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 3 2" xfId="130"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 4" xfId="131"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 4 2" xfId="132"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 5" xfId="133"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 6" xfId="134"/>
-    <cellStyle name="20% - 强调文字颜色 5 3" xfId="135"/>
-    <cellStyle name="20% - 强调文字颜色 5 3 2" xfId="136"/>
-    <cellStyle name="20% - 强调文字颜色 5 3 3" xfId="137"/>
-    <cellStyle name="20% - 强调文字颜色 5 4" xfId="138"/>
-    <cellStyle name="20% - 强调文字颜色 5 4 2" xfId="139"/>
-    <cellStyle name="20% - 强调文字颜色 5 5" xfId="140"/>
-    <cellStyle name="20% - 强调文字颜色 5 5 2" xfId="141"/>
-    <cellStyle name="20% - 强调文字颜色 5 6" xfId="142"/>
-    <cellStyle name="20% - 强调文字颜色 5 7" xfId="143"/>
-    <cellStyle name="20% - 强调文字颜色 6 2" xfId="144"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="145"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2 2" xfId="146"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2 3" xfId="147"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 3" xfId="148"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 3 2" xfId="149"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 4" xfId="150"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 4 2" xfId="151"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 5" xfId="152"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 6" xfId="153"/>
-    <cellStyle name="20% - 强调文字颜色 6 3" xfId="154"/>
-    <cellStyle name="20% - 强调文字颜色 6 3 2" xfId="155"/>
-    <cellStyle name="20% - 强调文字颜色 6 3 3" xfId="156"/>
-    <cellStyle name="20% - 强调文字颜色 6 4" xfId="157"/>
-    <cellStyle name="20% - 强调文字颜色 6 4 2" xfId="158"/>
-    <cellStyle name="20% - 强调文字颜色 6 5" xfId="159"/>
-    <cellStyle name="20% - 强调文字颜色 6 5 2" xfId="160"/>
-    <cellStyle name="20% - 强调文字颜色 6 6" xfId="161"/>
-    <cellStyle name="20% - 强调文字颜色 6 7" xfId="162"/>
-    <cellStyle name="40% - 强调文字颜色 1 2" xfId="163"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="164"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2 2" xfId="165"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2 3" xfId="166"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 3" xfId="167"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 3 2" xfId="168"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 4" xfId="169"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 4 2" xfId="170"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 5" xfId="171"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 6" xfId="172"/>
-    <cellStyle name="40% - 强调文字颜色 1 3" xfId="173"/>
-    <cellStyle name="40% - 强调文字颜色 1 3 2" xfId="174"/>
-    <cellStyle name="40% - 强调文字颜色 1 3 3" xfId="175"/>
-    <cellStyle name="40% - 强调文字颜色 1 4" xfId="176"/>
-    <cellStyle name="40% - 强调文字颜色 1 4 2" xfId="177"/>
-    <cellStyle name="40% - 强调文字颜色 1 5" xfId="178"/>
-    <cellStyle name="40% - 强调文字颜色 1 5 2" xfId="179"/>
-    <cellStyle name="40% - 强调文字颜色 1 6" xfId="180"/>
-    <cellStyle name="40% - 强调文字颜色 1 7" xfId="181"/>
-    <cellStyle name="40% - 强调文字颜色 2 2" xfId="182"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="183"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2 2" xfId="184"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2 3" xfId="185"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 3" xfId="186"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 3 2" xfId="187"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 4" xfId="188"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 4 2" xfId="189"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 5" xfId="190"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 6" xfId="191"/>
-    <cellStyle name="40% - 强调文字颜色 2 3" xfId="192"/>
-    <cellStyle name="40% - 强调文字颜色 2 3 2" xfId="193"/>
-    <cellStyle name="40% - 强调文字颜色 2 3 3" xfId="194"/>
-    <cellStyle name="40% - 强调文字颜色 2 4" xfId="195"/>
-    <cellStyle name="40% - 强调文字颜色 2 4 2" xfId="196"/>
-    <cellStyle name="40% - 强调文字颜色 2 5" xfId="197"/>
-    <cellStyle name="40% - 强调文字颜色 2 5 2" xfId="198"/>
-    <cellStyle name="40% - 强调文字颜色 2 6" xfId="199"/>
-    <cellStyle name="40% - 强调文字颜色 2 7" xfId="200"/>
-    <cellStyle name="40% - 强调文字颜色 3 2" xfId="201"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="202"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2 2" xfId="203"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2 3" xfId="204"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 3" xfId="205"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 3 2" xfId="206"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 4" xfId="207"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 4 2" xfId="208"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 5" xfId="209"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 6" xfId="210"/>
-    <cellStyle name="40% - 强调文字颜色 3 3" xfId="211"/>
-    <cellStyle name="40% - 强调文字颜色 3 3 2" xfId="212"/>
-    <cellStyle name="40% - 强调文字颜色 3 3 3" xfId="213"/>
-    <cellStyle name="40% - 强调文字颜色 3 4" xfId="214"/>
-    <cellStyle name="40% - 强调文字颜色 3 4 2" xfId="215"/>
-    <cellStyle name="40% - 强调文字颜色 3 5" xfId="216"/>
-    <cellStyle name="40% - 强调文字颜色 3 5 2" xfId="217"/>
-    <cellStyle name="40% - 强调文字颜色 3 6" xfId="218"/>
-    <cellStyle name="40% - 强调文字颜色 3 7" xfId="219"/>
-    <cellStyle name="40% - 强调文字颜色 4 2" xfId="220"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="221"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2 2" xfId="222"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2 3" xfId="223"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 3" xfId="224"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 3 2" xfId="225"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 4" xfId="226"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 4 2" xfId="227"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 5" xfId="228"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 6" xfId="229"/>
-    <cellStyle name="40% - 强调文字颜色 4 3" xfId="230"/>
-    <cellStyle name="40% - 强调文字颜色 4 3 2" xfId="231"/>
-    <cellStyle name="40% - 强调文字颜色 4 3 3" xfId="232"/>
-    <cellStyle name="40% - 强调文字颜色 4 4" xfId="233"/>
-    <cellStyle name="40% - 强调文字颜色 4 4 2" xfId="234"/>
-    <cellStyle name="40% - 强调文字颜色 4 5" xfId="235"/>
-    <cellStyle name="40% - 强调文字颜色 4 5 2" xfId="236"/>
-    <cellStyle name="40% - 强调文字颜色 4 6" xfId="237"/>
-    <cellStyle name="40% - 强调文字颜色 4 7" xfId="238"/>
-    <cellStyle name="40% - 强调文字颜色 5 2" xfId="239"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="240"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2 2" xfId="241"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2 3" xfId="242"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 3" xfId="243"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 3 2" xfId="244"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 4" xfId="245"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 4 2" xfId="246"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 5" xfId="247"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 6" xfId="248"/>
-    <cellStyle name="40% - 强调文字颜色 5 3" xfId="249"/>
-    <cellStyle name="40% - 强调文字颜色 5 3 2" xfId="250"/>
-    <cellStyle name="40% - 强调文字颜色 5 3 3" xfId="251"/>
-    <cellStyle name="40% - 强调文字颜色 5 4" xfId="252"/>
-    <cellStyle name="40% - 强调文字颜色 5 4 2" xfId="253"/>
-    <cellStyle name="40% - 强调文字颜色 5 5" xfId="254"/>
-    <cellStyle name="40% - 强调文字颜色 5 5 2" xfId="255"/>
-    <cellStyle name="40% - 强调文字颜色 5 6" xfId="256"/>
-    <cellStyle name="40% - 强调文字颜色 5 7" xfId="257"/>
-    <cellStyle name="40% - 强调文字颜色 6 2" xfId="258"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="259"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2 2" xfId="260"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2 3" xfId="261"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 3" xfId="262"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 3 2" xfId="263"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 4" xfId="264"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 4 2" xfId="265"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 5" xfId="266"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 6" xfId="267"/>
-    <cellStyle name="40% - 强调文字颜色 6 3" xfId="268"/>
-    <cellStyle name="40% - 强调文字颜色 6 3 2" xfId="269"/>
-    <cellStyle name="40% - 强调文字颜色 6 3 3" xfId="270"/>
-    <cellStyle name="40% - 强调文字颜色 6 4" xfId="271"/>
-    <cellStyle name="40% - 强调文字颜色 6 4 2" xfId="272"/>
-    <cellStyle name="40% - 强调文字颜色 6 5" xfId="273"/>
-    <cellStyle name="40% - 强调文字颜色 6 5 2" xfId="274"/>
-    <cellStyle name="40% - 强调文字颜色 6 6" xfId="275"/>
-    <cellStyle name="40% - 强调文字颜色 6 7" xfId="276"/>
-    <cellStyle name="常规 2" xfId="277"/>
-    <cellStyle name="常规 2 2" xfId="278"/>
-    <cellStyle name="常规 2 3" xfId="279"/>
-    <cellStyle name="常规 2 3 2" xfId="280"/>
-    <cellStyle name="常规 2 3 2 2" xfId="281"/>
-    <cellStyle name="常规 2 3 2 2 2" xfId="282"/>
-    <cellStyle name="常规 2 3 2 2 2 2" xfId="283"/>
-    <cellStyle name="常规 2 3 2 2 2 3" xfId="284"/>
-    <cellStyle name="常规 2 3 2 2 3" xfId="285"/>
-    <cellStyle name="常规 2 3 2 2 3 2" xfId="286"/>
-    <cellStyle name="常规 2 3 2 2 4" xfId="287"/>
-    <cellStyle name="常规 2 3 2 2 4 2" xfId="288"/>
-    <cellStyle name="常规 2 3 2 2 5" xfId="289"/>
-    <cellStyle name="常规 2 3 2 2 6" xfId="290"/>
-    <cellStyle name="常规 2 3 2 3" xfId="291"/>
-    <cellStyle name="常规 2 3 2 3 2" xfId="292"/>
-    <cellStyle name="常规 2 3 2 3 3" xfId="293"/>
-    <cellStyle name="常规 2 3 2 4" xfId="294"/>
-    <cellStyle name="常规 2 3 2 4 2" xfId="295"/>
-    <cellStyle name="常规 2 3 2 5" xfId="296"/>
-    <cellStyle name="常规 2 3 2 5 2" xfId="297"/>
-    <cellStyle name="常规 2 3 2 6" xfId="298"/>
-    <cellStyle name="常规 2 3 2 7" xfId="299"/>
-    <cellStyle name="常规 2 3 3" xfId="300"/>
-    <cellStyle name="常规 2 3 3 2" xfId="301"/>
-    <cellStyle name="常规 2 3 3 2 2" xfId="302"/>
-    <cellStyle name="常规 2 3 3 2 3" xfId="303"/>
-    <cellStyle name="常规 2 3 3 3" xfId="304"/>
-    <cellStyle name="常规 2 3 3 3 2" xfId="305"/>
-    <cellStyle name="常规 2 3 3 4" xfId="306"/>
-    <cellStyle name="常规 2 3 3 4 2" xfId="307"/>
-    <cellStyle name="常规 2 3 3 5" xfId="308"/>
-    <cellStyle name="常规 2 3 3 6" xfId="309"/>
-    <cellStyle name="常规 2 3 4" xfId="310"/>
-    <cellStyle name="常规 2 3 4 2" xfId="311"/>
-    <cellStyle name="常规 2 3 4 3" xfId="312"/>
-    <cellStyle name="常规 2 3 5" xfId="313"/>
-    <cellStyle name="常规 2 3 5 2" xfId="314"/>
-    <cellStyle name="常规 2 3 6" xfId="315"/>
-    <cellStyle name="常规 2 3 6 2" xfId="316"/>
-    <cellStyle name="常规 2 3 7" xfId="317"/>
-    <cellStyle name="常规 2 3 8" xfId="318"/>
-    <cellStyle name="常规 3" xfId="319"/>
-    <cellStyle name="常规 4" xfId="320"/>
-    <cellStyle name="常规 5" xfId="321"/>
-    <cellStyle name="常规 5 2" xfId="322"/>
-    <cellStyle name="常规 5 2 2" xfId="323"/>
-    <cellStyle name="常规 5 2 2 2" xfId="324"/>
-    <cellStyle name="常规 5 2 2 3" xfId="325"/>
-    <cellStyle name="常规 5 2 3" xfId="326"/>
-    <cellStyle name="常规 5 2 3 2" xfId="327"/>
-    <cellStyle name="常规 5 2 4" xfId="328"/>
-    <cellStyle name="常规 5 2 4 2" xfId="329"/>
-    <cellStyle name="常规 5 2 5" xfId="330"/>
-    <cellStyle name="常规 5 2 6" xfId="331"/>
-    <cellStyle name="常规 5 3" xfId="332"/>
-    <cellStyle name="常规 5 3 2" xfId="333"/>
-    <cellStyle name="常规 5 3 3" xfId="334"/>
-    <cellStyle name="常规 5 4" xfId="335"/>
-    <cellStyle name="常规 5 4 2" xfId="336"/>
-    <cellStyle name="常规 5 5" xfId="337"/>
-    <cellStyle name="常规 5 5 2" xfId="338"/>
-    <cellStyle name="常规 5 6" xfId="339"/>
-    <cellStyle name="常规 5 7" xfId="340"/>
-    <cellStyle name="注释 2" xfId="341"/>
-    <cellStyle name="注释 2 2" xfId="342"/>
-    <cellStyle name="注释 2 2 2" xfId="343"/>
-    <cellStyle name="注释 2 2 2 2" xfId="344"/>
-    <cellStyle name="注释 2 2 2 3" xfId="345"/>
-    <cellStyle name="注释 2 2 3" xfId="346"/>
-    <cellStyle name="注释 2 2 3 2" xfId="347"/>
-    <cellStyle name="注释 2 2 4" xfId="348"/>
-    <cellStyle name="注释 2 2 4 2" xfId="349"/>
-    <cellStyle name="注释 2 2 5" xfId="350"/>
-    <cellStyle name="注释 2 2 6" xfId="351"/>
-    <cellStyle name="注释 2 3" xfId="352"/>
-    <cellStyle name="注释 2 3 2" xfId="353"/>
-    <cellStyle name="注释 2 3 3" xfId="354"/>
-    <cellStyle name="注释 2 4" xfId="355"/>
-    <cellStyle name="注释 2 4 2" xfId="356"/>
-    <cellStyle name="注释 2 5" xfId="357"/>
-    <cellStyle name="注释 2 5 2" xfId="358"/>
-    <cellStyle name="注释 2 6" xfId="359"/>
-    <cellStyle name="注释 2 7" xfId="360"/>
+    <cellStyle name="常规 2" xfId="229" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
+    <cellStyle name="常规 2 2" xfId="230" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
+    <cellStyle name="常规 2 3" xfId="231" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
+    <cellStyle name="常规 2 3 2" xfId="232" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
+    <cellStyle name="常规 2 3 2 2" xfId="233" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
+    <cellStyle name="常规 2 3 2 2 2" xfId="234" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
+    <cellStyle name="常规 2 3 2 2 2 2" xfId="235" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
+    <cellStyle name="常规 2 3 2 2 2 3" xfId="236" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
+    <cellStyle name="常规 2 3 2 2 3" xfId="237" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
+    <cellStyle name="常规 2 3 2 2 3 2" xfId="238" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
+    <cellStyle name="常规 2 3 2 2 4" xfId="239" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
+    <cellStyle name="常规 2 3 2 2 4 2" xfId="240" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
+    <cellStyle name="常规 2 3 2 2 5" xfId="241" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
+    <cellStyle name="常规 2 3 2 2 6" xfId="242" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
+    <cellStyle name="常规 2 3 2 3" xfId="243" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
+    <cellStyle name="常规 2 3 2 3 2" xfId="244" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
+    <cellStyle name="常规 2 3 2 3 3" xfId="245" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
+    <cellStyle name="常规 2 3 2 4" xfId="246" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
+    <cellStyle name="常规 2 3 2 4 2" xfId="247" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
+    <cellStyle name="常规 2 3 2 5" xfId="248" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
+    <cellStyle name="常规 2 3 2 5 2" xfId="249" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
+    <cellStyle name="常规 2 3 2 6" xfId="250" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
+    <cellStyle name="常规 2 3 2 7" xfId="251" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
+    <cellStyle name="常规 2 3 3" xfId="252" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
+    <cellStyle name="常规 2 3 3 2" xfId="253" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
+    <cellStyle name="常规 2 3 3 2 2" xfId="254" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
+    <cellStyle name="常规 2 3 3 2 3" xfId="255" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
+    <cellStyle name="常规 2 3 3 3" xfId="256" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
+    <cellStyle name="常规 2 3 3 3 2" xfId="257" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
+    <cellStyle name="常规 2 3 3 4" xfId="258" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
+    <cellStyle name="常规 2 3 3 4 2" xfId="259" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
+    <cellStyle name="常规 2 3 3 5" xfId="260" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
+    <cellStyle name="常规 2 3 3 6" xfId="261" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
+    <cellStyle name="常规 2 3 4" xfId="262" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
+    <cellStyle name="常规 2 3 4 2" xfId="263" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
+    <cellStyle name="常规 2 3 4 3" xfId="264" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
+    <cellStyle name="常规 2 3 5" xfId="265" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
+    <cellStyle name="常规 2 3 5 2" xfId="266" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
+    <cellStyle name="常规 2 3 6" xfId="267" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
+    <cellStyle name="常规 2 3 6 2" xfId="268" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
+    <cellStyle name="常规 2 3 7" xfId="269" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
+    <cellStyle name="常规 2 3 8" xfId="270" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
+    <cellStyle name="常规 3" xfId="271" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
+    <cellStyle name="常规 4" xfId="272" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
+    <cellStyle name="常规 5" xfId="273" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
+    <cellStyle name="常规 5 2" xfId="274" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
+    <cellStyle name="常规 5 2 2" xfId="275" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
+    <cellStyle name="常规 5 2 2 2" xfId="276" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
+    <cellStyle name="常规 5 2 2 3" xfId="277" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
+    <cellStyle name="常规 5 2 3" xfId="278" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
+    <cellStyle name="常规 5 2 3 2" xfId="279" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
+    <cellStyle name="常规 5 2 4" xfId="280" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
+    <cellStyle name="常规 5 2 4 2" xfId="281" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
+    <cellStyle name="常规 5 2 5" xfId="282" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
+    <cellStyle name="常规 5 2 6" xfId="283" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
+    <cellStyle name="常规 5 3" xfId="284" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
+    <cellStyle name="常规 5 3 2" xfId="285" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
+    <cellStyle name="常规 5 3 3" xfId="286" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
+    <cellStyle name="常规 5 4" xfId="287" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
+    <cellStyle name="常规 5 4 2" xfId="288" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
+    <cellStyle name="常规 5 5" xfId="289" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
+    <cellStyle name="常规 5 5 2" xfId="290" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
+    <cellStyle name="常规 5 6" xfId="291" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
+    <cellStyle name="常规 5 7" xfId="292" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
+    <cellStyle name="注释 2" xfId="293" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
+    <cellStyle name="注释 2 2" xfId="294" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
+    <cellStyle name="注释 2 2 2" xfId="295" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
+    <cellStyle name="注释 2 2 2 2" xfId="296" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
+    <cellStyle name="注释 2 2 2 3" xfId="297" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
+    <cellStyle name="注释 2 2 3" xfId="298" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
+    <cellStyle name="注释 2 2 3 2" xfId="299" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
+    <cellStyle name="注释 2 2 4" xfId="300" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
+    <cellStyle name="注释 2 2 4 2" xfId="301" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
+    <cellStyle name="注释 2 2 5" xfId="302" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
+    <cellStyle name="注释 2 2 6" xfId="303" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
+    <cellStyle name="注释 2 3" xfId="304" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
+    <cellStyle name="注释 2 3 2" xfId="305" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
+    <cellStyle name="注释 2 3 3" xfId="306" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
+    <cellStyle name="注释 2 4" xfId="307" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
+    <cellStyle name="注释 2 4 2" xfId="308" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
+    <cellStyle name="注释 2 5" xfId="309" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
+    <cellStyle name="注释 2 5 2" xfId="310" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
+    <cellStyle name="注释 2 6" xfId="311" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
+    <cellStyle name="注释 2 7" xfId="312" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <i val="0"/>
       </font>
       <fill>
@@ -3075,6 +2491,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3104,19 +2523,19 @@
     </xsd:schema>
   </Schema>
   <Map ID="1" Name="DateArea_映射" RootElement="DateArea" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true">
-    <DataBinding ConnectionID="1" FileBinding="true" DataBindingLoadMode="1"/>
+    <DataBinding FileBinding="true" ConnectionID="1" DataBindingLoadMode="1"/>
   </Map>
 </MapInfo>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C3:G20" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="C3:G20" totalsRowShown="0">
   <tableColumns count="5">
-    <tableColumn id="1" name="Id"/>
-    <tableColumn id="2" name="活动类型"/>
-    <tableColumn id="3" name="Icon显示"/>
-    <tableColumn id="4" name="参数_1"/>
-    <tableColumn id="5" name="参数_2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="活动类型"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Icon显示"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="参数_1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="参数_2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3401,14 +2820,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C1:J212"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="5" width="21.625" customWidth="1"/>
     <col min="6" max="6" width="26.125" customWidth="1"/>
@@ -3417,8 +2836,8 @@
     <col min="9" max="9" width="40.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25"/>
-    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="1" spans="3:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -3441,7 +2860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="4" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -3464,7 +2883,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="5" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
@@ -3487,7 +2906,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="6" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="6">
         <v>2001</v>
       </c>
@@ -3510,7 +2929,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="7" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="6">
         <v>2003</v>
       </c>
@@ -3533,7 +2952,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="8" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="6">
         <v>2004</v>
       </c>
@@ -3556,7 +2975,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="9" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C9" s="6">
         <v>2005</v>
       </c>
@@ -3579,7 +2998,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="10" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C10" s="6">
         <v>2006</v>
       </c>
@@ -3602,7 +3021,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="11" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C11" s="6">
         <v>2007</v>
       </c>
@@ -3625,7 +3044,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="12" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="6">
         <v>2008</v>
       </c>
@@ -3648,7 +3067,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="13" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="6">
         <v>2009</v>
       </c>
@@ -3671,7 +3090,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="14" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="6">
         <v>2010</v>
       </c>
@@ -3694,7 +3113,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="15" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="6">
         <v>2011</v>
       </c>
@@ -3717,7 +3136,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="16" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="6">
         <v>2012</v>
       </c>
@@ -3740,7 +3159,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="17" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="6">
         <v>2013</v>
       </c>
@@ -3763,7 +3182,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="18" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="6">
         <v>2014</v>
       </c>
@@ -3786,7 +3205,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="19" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="6">
         <v>2015</v>
       </c>
@@ -3809,7 +3228,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="20" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="6">
         <v>2016</v>
       </c>
@@ -3832,7 +3251,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="3:9">
+    <row r="21" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="11">
         <v>10001</v>
       </c>
@@ -3846,15 +3265,15 @@
       <c r="G21" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H21" s="11" t="s">
-        <v>49</v>
+      <c r="H21" s="18" t="s">
+        <v>232</v>
       </c>
       <c r="I21" s="11" t="str">
         <f>F21&amp;"级礼包"</f>
         <v>5级礼包</v>
       </c>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="3:9">
+    <row r="22" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="11">
         <v>10002</v>
       </c>
@@ -3868,15 +3287,15 @@
       <c r="G22" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="11" t="s">
-        <v>50</v>
+      <c r="H22" s="18" t="s">
+        <v>232</v>
       </c>
       <c r="I22" s="11" t="str">
         <f t="shared" ref="I22:I26" si="0">F22&amp;"级礼包"</f>
         <v>10级礼包</v>
       </c>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="3:9">
+    <row r="23" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C23" s="11">
         <v>10003</v>
       </c>
@@ -3890,15 +3309,15 @@
       <c r="G23" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="11" t="s">
-        <v>51</v>
+      <c r="H23" s="18" t="s">
+        <v>233</v>
       </c>
       <c r="I23" s="11" t="str">
         <f t="shared" si="0"/>
         <v>15级礼包</v>
       </c>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="3:9">
+    <row r="24" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="11">
         <v>10004</v>
       </c>
@@ -3912,15 +3331,15 @@
       <c r="G24" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H24" s="11" t="s">
-        <v>52</v>
+      <c r="H24" s="18" t="s">
+        <v>230</v>
       </c>
       <c r="I24" s="11" t="str">
         <f t="shared" si="0"/>
         <v>20级礼包</v>
       </c>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="3:9">
+    <row r="25" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="11">
         <v>10005</v>
       </c>
@@ -3934,15 +3353,15 @@
       <c r="G25" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>53</v>
+      <c r="H25" s="18" t="s">
+        <v>230</v>
       </c>
       <c r="I25" s="11" t="str">
         <f t="shared" si="0"/>
         <v>25级礼包</v>
       </c>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="3:9">
+    <row r="26" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C26" s="11">
         <v>10006</v>
       </c>
@@ -3956,15 +3375,15 @@
       <c r="G26" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H26" s="11" t="s">
-        <v>54</v>
+      <c r="H26" s="18" t="s">
+        <v>231</v>
       </c>
       <c r="I26" s="11" t="str">
         <f t="shared" si="0"/>
         <v>30级礼包</v>
       </c>
     </row>
-    <row r="27" ht="20.1" customHeight="1" spans="3:9">
+    <row r="27" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="11">
         <v>21001</v>
       </c>
@@ -3985,7 +3404,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="3:9">
+    <row r="28" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="11">
         <v>21002</v>
       </c>
@@ -4006,7 +3425,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" ht="20.1" customHeight="1" spans="3:9">
+    <row r="29" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C29" s="11">
         <v>21003</v>
       </c>
@@ -4027,7 +3446,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" ht="20.1" customHeight="1" spans="3:9">
+    <row r="30" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C30" s="11">
         <v>21004</v>
       </c>
@@ -4048,7 +3467,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" ht="20.1" customHeight="1" spans="3:9">
+    <row r="31" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C31" s="11">
         <v>21005</v>
       </c>
@@ -4069,7 +3488,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" ht="20.1" customHeight="1" spans="3:9">
+    <row r="32" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C32" s="11">
         <v>21006</v>
       </c>
@@ -4090,7 +3509,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" ht="20.1" customHeight="1" spans="3:9">
+    <row r="33" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C33" s="11">
         <v>21007</v>
       </c>
@@ -4111,7 +3530,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" ht="20.1" customHeight="1" spans="3:9">
+    <row r="34" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="11">
         <v>21008</v>
       </c>
@@ -4132,7 +3551,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" ht="20.1" customHeight="1" spans="3:9">
+    <row r="35" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="11">
         <v>21009</v>
       </c>
@@ -4153,7 +3572,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" ht="20.1" customHeight="1" spans="3:9">
+    <row r="36" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C36" s="11">
         <v>21010</v>
       </c>
@@ -4174,7 +3593,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" ht="20.1" customHeight="1" spans="3:9">
+    <row r="37" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C37" s="11">
         <v>21011</v>
       </c>
@@ -4195,7 +3614,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" ht="20.1" customHeight="1" spans="3:9">
+    <row r="38" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C38" s="11">
         <v>22001</v>
       </c>
@@ -4216,7 +3635,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" ht="20.1" customHeight="1" spans="3:9">
+    <row r="39" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C39" s="11">
         <v>22002</v>
       </c>
@@ -4237,7 +3656,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" ht="20.1" customHeight="1" spans="3:9">
+    <row r="40" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C40" s="11">
         <v>22003</v>
       </c>
@@ -4258,7 +3677,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" ht="20.1" customHeight="1" spans="3:9">
+    <row r="41" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="11">
         <v>22004</v>
       </c>
@@ -4279,7 +3698,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" ht="20.1" customHeight="1" spans="3:9">
+    <row r="42" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="11">
         <v>22005</v>
       </c>
@@ -4300,7 +3719,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" ht="20.1" customHeight="1" spans="3:9">
+    <row r="43" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="11">
         <v>22006</v>
       </c>
@@ -4321,7 +3740,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" ht="20.1" customHeight="1" spans="3:9">
+    <row r="44" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="11">
         <v>22007</v>
       </c>
@@ -4342,7 +3761,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" ht="20.1" customHeight="1" spans="3:9">
+    <row r="45" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="11">
         <v>22008</v>
       </c>
@@ -4363,7 +3782,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" ht="20.1" customHeight="1" spans="3:9">
+    <row r="46" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="11">
         <v>22009</v>
       </c>
@@ -4384,7 +3803,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="47" ht="20.1" customHeight="1" spans="3:9">
+    <row r="47" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="11">
         <v>22010</v>
       </c>
@@ -4405,7 +3824,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="48" ht="20.1" customHeight="1" spans="3:9">
+    <row r="48" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="11">
         <v>22011</v>
       </c>
@@ -4426,7 +3845,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="49" ht="20.1" customHeight="1" spans="3:9">
+    <row r="49" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C49" s="11">
         <v>23001</v>
       </c>
@@ -4445,7 +3864,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" ht="20.1" customHeight="1" spans="3:9">
+    <row r="50" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C50" s="11">
         <v>23002</v>
       </c>
@@ -4464,7 +3883,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" ht="20.1" customHeight="1" spans="3:9">
+    <row r="51" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C51" s="11">
         <v>23003</v>
       </c>
@@ -4483,7 +3902,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="52" ht="20.1" customHeight="1" spans="3:9">
+    <row r="52" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="11">
         <v>23004</v>
       </c>
@@ -4502,7 +3921,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="53" ht="20.1" customHeight="1" spans="3:9">
+    <row r="53" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C53" s="11">
         <v>23005</v>
       </c>
@@ -4521,7 +3940,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" ht="20.1" customHeight="1" spans="3:9">
+    <row r="54" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="11">
         <v>23006</v>
       </c>
@@ -4540,7 +3959,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="55" ht="20.1" customHeight="1" spans="3:9">
+    <row r="55" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="11">
         <v>23007</v>
       </c>
@@ -4559,7 +3978,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="56" ht="20.1" customHeight="1" spans="3:9">
+    <row r="56" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="11">
         <v>23008</v>
       </c>
@@ -4578,7 +3997,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="57" ht="20.1" customHeight="1" spans="3:9">
+    <row r="57" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C57" s="11">
         <v>23009</v>
       </c>
@@ -4597,7 +4016,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="58" ht="20.1" customHeight="1" spans="3:9">
+    <row r="58" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="11">
         <v>23010</v>
       </c>
@@ -4616,7 +4035,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="59" ht="20.1" customHeight="1" spans="3:9">
+    <row r="59" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="11">
         <v>23011</v>
       </c>
@@ -4635,7 +4054,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="60" ht="20.1" customHeight="1" spans="3:9">
+    <row r="60" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="11">
         <v>23012</v>
       </c>
@@ -4654,7 +4073,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="61" ht="20.1" customHeight="1" spans="3:9">
+    <row r="61" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="11">
         <v>23013</v>
       </c>
@@ -4673,7 +4092,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="62" ht="20.1" customHeight="1" spans="3:9">
+    <row r="62" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="11">
         <v>23014</v>
       </c>
@@ -4692,7 +4111,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="63" ht="20.1" customHeight="1" spans="3:9">
+    <row r="63" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C63" s="11">
         <v>23015</v>
       </c>
@@ -4711,7 +4130,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="64" ht="20.1" customHeight="1" spans="3:9">
+    <row r="64" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C64" s="11">
         <v>23016</v>
       </c>
@@ -4730,7 +4149,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="65" ht="20.1" customHeight="1" spans="3:9">
+    <row r="65" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C65" s="11">
         <v>23017</v>
       </c>
@@ -4749,7 +4168,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="66" ht="20.1" customHeight="1" spans="3:9">
+    <row r="66" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C66" s="11">
         <v>23018</v>
       </c>
@@ -4768,7 +4187,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="67" ht="20.1" customHeight="1" spans="3:9">
+    <row r="67" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C67" s="11">
         <v>23019</v>
       </c>
@@ -4787,7 +4206,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="68" ht="20.1" customHeight="1" spans="3:9">
+    <row r="68" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C68" s="11">
         <v>23020</v>
       </c>
@@ -4806,7 +4225,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="69" ht="20.1" customHeight="1" spans="3:9">
+    <row r="69" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C69" s="11">
         <v>23021</v>
       </c>
@@ -4825,7 +4244,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="70" ht="20.1" customHeight="1" spans="3:9">
+    <row r="70" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C70" s="11">
         <v>23022</v>
       </c>
@@ -4844,7 +4263,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="71" ht="20.1" customHeight="1" spans="3:9">
+    <row r="71" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C71" s="11">
         <v>23023</v>
       </c>
@@ -4863,7 +4282,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="72" ht="20.1" customHeight="1" spans="3:9">
+    <row r="72" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C72" s="11">
         <v>23024</v>
       </c>
@@ -4882,7 +4301,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="73" ht="20.1" customHeight="1" spans="3:9">
+    <row r="73" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C73" s="11">
         <v>23025</v>
       </c>
@@ -4901,7 +4320,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="74" ht="20.1" customHeight="1" spans="3:9">
+    <row r="74" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C74" s="11">
         <v>23026</v>
       </c>
@@ -4920,7 +4339,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" ht="20.1" customHeight="1" spans="3:9">
+    <row r="75" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C75" s="11">
         <v>23027</v>
       </c>
@@ -4939,7 +4358,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="76" ht="20.1" customHeight="1" spans="3:9">
+    <row r="76" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C76" s="11">
         <v>23028</v>
       </c>
@@ -4958,7 +4377,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="77" ht="20.1" customHeight="1" spans="3:9">
+    <row r="77" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C77" s="11">
         <v>23029</v>
       </c>
@@ -4977,7 +4396,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="78" ht="20.1" customHeight="1" spans="3:9">
+    <row r="78" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C78" s="11">
         <v>23030</v>
       </c>
@@ -4996,7 +4415,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="79" ht="20.1" customHeight="1" spans="3:9">
+    <row r="79" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C79" s="11">
         <v>24001</v>
       </c>
@@ -5017,7 +4436,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="80" ht="20.1" customHeight="1" spans="3:9">
+    <row r="80" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C80" s="11">
         <v>24002</v>
       </c>
@@ -5038,7 +4457,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" ht="20.1" customHeight="1" spans="3:9">
+    <row r="81" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C81" s="11">
         <v>24003</v>
       </c>
@@ -5059,7 +4478,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="82" ht="20.1" customHeight="1" spans="3:9">
+    <row r="82" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C82" s="11">
         <v>24004</v>
       </c>
@@ -5080,7 +4499,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="83" ht="20.1" customHeight="1" spans="3:9">
+    <row r="83" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C83" s="11">
         <v>24005</v>
       </c>
@@ -5101,7 +4520,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="84" ht="20.1" customHeight="1" spans="3:9">
+    <row r="84" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C84" s="11">
         <v>24006</v>
       </c>
@@ -5122,7 +4541,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="85" ht="20.1" customHeight="1" spans="3:9">
+    <row r="85" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C85" s="11">
         <v>24007</v>
       </c>
@@ -5143,7 +4562,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="86" ht="20.1" customHeight="1" spans="3:9">
+    <row r="86" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C86" s="11">
         <v>24008</v>
       </c>
@@ -5164,7 +4583,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="87" ht="20.1" customHeight="1" spans="3:9">
+    <row r="87" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C87" s="11">
         <v>24009</v>
       </c>
@@ -5185,7 +4604,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="88" ht="20.1" customHeight="1" spans="3:9">
+    <row r="88" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C88" s="11">
         <v>24010</v>
       </c>
@@ -5206,7 +4625,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="89" ht="20.1" customHeight="1" spans="3:9">
+    <row r="89" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C89" s="11">
         <v>24011</v>
       </c>
@@ -5227,7 +4646,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="90" ht="20.1" customHeight="1" spans="3:9">
+    <row r="90" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C90" s="11">
         <v>24012</v>
       </c>
@@ -5248,7 +4667,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="91" ht="20.1" customHeight="1" spans="3:9">
+    <row r="91" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C91" s="11">
         <v>24013</v>
       </c>
@@ -5269,7 +4688,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="92" ht="20.1" customHeight="1" spans="3:9">
+    <row r="92" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C92" s="11">
         <v>24014</v>
       </c>
@@ -5290,7 +4709,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="93" ht="20.1" customHeight="1" spans="3:9">
+    <row r="93" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C93" s="11">
         <v>24015</v>
       </c>
@@ -5311,7 +4730,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="94" ht="20.1" customHeight="1" spans="3:9">
+    <row r="94" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C94" s="11">
         <v>24016</v>
       </c>
@@ -5332,7 +4751,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="95" ht="20.1" customHeight="1" spans="3:9">
+    <row r="95" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C95" s="11">
         <v>24017</v>
       </c>
@@ -5353,7 +4772,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="96" ht="20.1" customHeight="1" spans="3:9">
+    <row r="96" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C96" s="11">
         <v>24018</v>
       </c>
@@ -5374,7 +4793,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="97" ht="20.1" customHeight="1" spans="3:9">
+    <row r="97" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C97" s="11">
         <v>24019</v>
       </c>
@@ -5395,7 +4814,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="98" ht="20.1" customHeight="1" spans="3:9">
+    <row r="98" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C98" s="11">
         <v>24020</v>
       </c>
@@ -5416,7 +4835,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="99" ht="20.1" customHeight="1" spans="3:9">
+    <row r="99" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C99" s="11">
         <v>24021</v>
       </c>
@@ -5437,7 +4856,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="100" ht="20.1" customHeight="1" spans="3:9">
+    <row r="100" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C100" s="11">
         <v>24022</v>
       </c>
@@ -5458,7 +4877,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="101" ht="20.1" customHeight="1" spans="3:9">
+    <row r="101" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C101" s="11">
         <v>24023</v>
       </c>
@@ -5479,7 +4898,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="102" ht="20.1" customHeight="1" spans="3:9">
+    <row r="102" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C102" s="11">
         <v>24024</v>
       </c>
@@ -5500,7 +4919,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="103" ht="20.1" customHeight="1" spans="3:9">
+    <row r="103" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C103" s="11">
         <v>24025</v>
       </c>
@@ -5521,7 +4940,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="104" ht="20.1" customHeight="1" spans="3:9">
+    <row r="104" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C104" s="11">
         <v>24026</v>
       </c>
@@ -5542,7 +4961,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="105" ht="20.1" customHeight="1" spans="3:9">
+    <row r="105" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C105" s="11">
         <v>24027</v>
       </c>
@@ -5563,7 +4982,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="106" ht="20.1" customHeight="1" spans="3:9">
+    <row r="106" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C106" s="11">
         <v>24028</v>
       </c>
@@ -5584,7 +5003,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="107" ht="20.1" customHeight="1" spans="3:9">
+    <row r="107" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C107" s="11">
         <v>25001</v>
       </c>
@@ -5603,7 +5022,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="108" ht="20.1" customHeight="1" spans="3:9">
+    <row r="108" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C108" s="11">
         <v>25002</v>
       </c>
@@ -5622,7 +5041,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="109" ht="20.1" customHeight="1" spans="3:9">
+    <row r="109" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C109" s="11">
         <v>25003</v>
       </c>
@@ -5641,7 +5060,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="110" ht="20.1" customHeight="1" spans="3:9">
+    <row r="110" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C110" s="11">
         <v>25004</v>
       </c>
@@ -5660,7 +5079,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="111" ht="20.1" customHeight="1" spans="3:9">
+    <row r="111" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C111" s="11">
         <v>25005</v>
       </c>
@@ -5679,7 +5098,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="112" ht="20.1" customHeight="1" spans="3:9">
+    <row r="112" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C112" s="11">
         <v>25006</v>
       </c>
@@ -5698,7 +5117,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="113" ht="20.1" customHeight="1" spans="3:9">
+    <row r="113" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C113" s="11">
         <v>25007</v>
       </c>
@@ -5717,7 +5136,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="114" ht="20.1" customHeight="1" spans="3:9">
+    <row r="114" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C114" s="11">
         <v>25008</v>
       </c>
@@ -5736,7 +5155,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="115" ht="20.1" customHeight="1" spans="3:9">
+    <row r="115" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C115" s="11">
         <v>25009</v>
       </c>
@@ -5755,7 +5174,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="116" ht="20.1" customHeight="1" spans="3:9">
+    <row r="116" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C116" s="11">
         <v>25010</v>
       </c>
@@ -5774,7 +5193,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="117" ht="20.1" customHeight="1" spans="3:9">
+    <row r="117" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C117" s="11">
         <v>25011</v>
       </c>
@@ -5793,7 +5212,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="118" ht="20.1" customHeight="1" spans="3:9">
+    <row r="118" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C118" s="11">
         <v>25012</v>
       </c>
@@ -5812,7 +5231,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="119" ht="20.1" customHeight="1" spans="3:9">
+    <row r="119" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C119" s="11">
         <v>25013</v>
       </c>
@@ -5831,7 +5250,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="120" ht="20.1" customHeight="1" spans="3:9">
+    <row r="120" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C120" s="11">
         <v>25014</v>
       </c>
@@ -5850,7 +5269,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="121" ht="20.1" customHeight="1" spans="3:9">
+    <row r="121" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C121" s="11">
         <v>25015</v>
       </c>
@@ -5869,7 +5288,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="122" ht="20.1" customHeight="1" spans="3:9">
+    <row r="122" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C122" s="11">
         <v>25016</v>
       </c>
@@ -5888,7 +5307,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="123" ht="20.1" customHeight="1" spans="3:9">
+    <row r="123" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C123" s="11">
         <v>25017</v>
       </c>
@@ -5907,7 +5326,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="124" ht="20.1" customHeight="1" spans="3:9">
+    <row r="124" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C124" s="11">
         <v>25018</v>
       </c>
@@ -5926,7 +5345,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="125" ht="20.1" customHeight="1" spans="3:9">
+    <row r="125" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C125" s="11">
         <v>25019</v>
       </c>
@@ -5945,7 +5364,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="126" ht="20.1" customHeight="1" spans="3:9">
+    <row r="126" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C126" s="11">
         <v>25020</v>
       </c>
@@ -5964,7 +5383,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="127" ht="20.1" customHeight="1" spans="3:9">
+    <row r="127" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C127" s="11">
         <v>25021</v>
       </c>
@@ -5983,7 +5402,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="128" ht="20.1" customHeight="1" spans="3:9">
+    <row r="128" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C128" s="11">
         <v>25022</v>
       </c>
@@ -6002,7 +5421,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="129" ht="20.1" customHeight="1" spans="3:9">
+    <row r="129" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C129" s="11">
         <v>25023</v>
       </c>
@@ -6021,7 +5440,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="130" ht="20.1" customHeight="1" spans="3:9">
+    <row r="130" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C130" s="11">
         <v>25024</v>
       </c>
@@ -6040,7 +5459,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="131" ht="20.1" customHeight="1" spans="3:9">
+    <row r="131" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C131" s="11">
         <v>25025</v>
       </c>
@@ -6059,7 +5478,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="132" ht="20.1" customHeight="1" spans="3:9">
+    <row r="132" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C132" s="11">
         <v>25026</v>
       </c>
@@ -6078,7 +5497,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="133" ht="20.1" customHeight="1" spans="3:9">
+    <row r="133" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C133" s="11">
         <v>25027</v>
       </c>
@@ -6097,7 +5516,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="134" ht="20.1" customHeight="1" spans="3:9">
+    <row r="134" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C134" s="11">
         <v>25028</v>
       </c>
@@ -6116,7 +5535,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="135" ht="20.1" customHeight="1" spans="3:9">
+    <row r="135" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C135" s="11">
         <v>25029</v>
       </c>
@@ -6135,7 +5554,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="136" ht="20.1" customHeight="1" spans="3:9">
+    <row r="136" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C136" s="11">
         <v>25030</v>
       </c>
@@ -6154,7 +5573,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="137" ht="20.1" customHeight="1" spans="3:9">
+    <row r="137" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C137" s="11">
         <v>26001</v>
       </c>
@@ -6173,7 +5592,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="138" ht="20.1" customHeight="1" spans="3:9">
+    <row r="138" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C138" s="11">
         <v>26002</v>
       </c>
@@ -6192,7 +5611,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="139" ht="20.1" customHeight="1" spans="3:9">
+    <row r="139" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C139" s="11">
         <v>26003</v>
       </c>
@@ -6211,7 +5630,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="140" ht="20.1" customHeight="1" spans="3:9">
+    <row r="140" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C140" s="11">
         <v>26004</v>
       </c>
@@ -6230,7 +5649,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="141" ht="20.1" customHeight="1" spans="3:9">
+    <row r="141" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C141" s="11">
         <v>27001</v>
       </c>
@@ -6249,7 +5668,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="142" ht="20.1" customHeight="1" spans="3:9">
+    <row r="142" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C142" s="11">
         <v>27002</v>
       </c>
@@ -6268,7 +5687,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="143" ht="20.1" customHeight="1" spans="3:9">
+    <row r="143" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C143" s="11">
         <v>27003</v>
       </c>
@@ -6287,7 +5706,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="144" ht="20.1" customHeight="1" spans="3:9">
+    <row r="144" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C144" s="11">
         <v>27004</v>
       </c>
@@ -6306,7 +5725,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="145" ht="20.1" customHeight="1" spans="3:9">
+    <row r="145" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C145" s="11">
         <v>30001</v>
       </c>
@@ -6327,7 +5746,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="146" ht="20.1" customHeight="1" spans="3:9">
+    <row r="146" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C146" s="11">
         <v>30002</v>
       </c>
@@ -6348,7 +5767,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="147" ht="20.1" customHeight="1" spans="3:9">
+    <row r="147" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C147" s="11">
         <v>30003</v>
       </c>
@@ -6369,7 +5788,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="148" ht="20.1" customHeight="1" spans="3:9">
+    <row r="148" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C148" s="11">
         <v>30004</v>
       </c>
@@ -6390,7 +5809,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="149" ht="20.1" customHeight="1" spans="3:10">
+    <row r="149" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C149" s="11">
         <v>30005</v>
       </c>
@@ -6412,7 +5831,7 @@
       </c>
       <c r="J149" s="12"/>
     </row>
-    <row r="150" ht="20.1" customHeight="1" spans="3:10">
+    <row r="150" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C150" s="11">
         <v>30006</v>
       </c>
@@ -6434,7 +5853,7 @@
       </c>
       <c r="J150" s="12"/>
     </row>
-    <row r="151" ht="20.1" customHeight="1" spans="3:10">
+    <row r="151" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C151" s="11">
         <v>30007</v>
       </c>
@@ -6456,7 +5875,7 @@
       </c>
       <c r="J151" s="12"/>
     </row>
-    <row r="152" ht="20.1" customHeight="1" spans="3:10">
+    <row r="152" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C152" s="11">
         <v>30008</v>
       </c>
@@ -6478,7 +5897,7 @@
       </c>
       <c r="J152" s="12"/>
     </row>
-    <row r="153" ht="20.1" customHeight="1" spans="3:10">
+    <row r="153" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C153" s="11">
         <v>30009</v>
       </c>
@@ -6500,7 +5919,7 @@
       </c>
       <c r="J153" s="12"/>
     </row>
-    <row r="154" ht="20.1" customHeight="1" spans="3:10">
+    <row r="154" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C154" s="11">
         <v>30010</v>
       </c>
@@ -6522,7 +5941,7 @@
       </c>
       <c r="J154" s="12"/>
     </row>
-    <row r="155" ht="20.1" customHeight="1" spans="3:9">
+    <row r="155" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C155" s="13">
         <v>31001</v>
       </c>
@@ -6543,7 +5962,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="156" ht="20.1" customHeight="1" spans="3:9">
+    <row r="156" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C156" s="13">
         <v>31002</v>
       </c>
@@ -6564,7 +5983,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="157" ht="20.1" customHeight="1" spans="3:9">
+    <row r="157" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C157" s="13">
         <v>31003</v>
       </c>
@@ -6585,7 +6004,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="158" ht="20.1" customHeight="1" spans="3:9">
+    <row r="158" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C158" s="13">
         <v>31004</v>
       </c>
@@ -6606,7 +6025,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="159" ht="20.1" customHeight="1" spans="3:9">
+    <row r="159" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C159" s="13">
         <v>31005</v>
       </c>
@@ -6627,7 +6046,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="160" ht="20.1" customHeight="1" spans="3:9">
+    <row r="160" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C160" s="13">
         <v>31006</v>
       </c>
@@ -6648,7 +6067,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="161" ht="20.1" customHeight="1" spans="3:9">
+    <row r="161" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C161" s="13">
         <v>31007</v>
       </c>
@@ -6669,7 +6088,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="162" ht="20.1" customHeight="1" spans="3:9">
+    <row r="162" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C162" s="13">
         <v>32001</v>
       </c>
@@ -6690,7 +6109,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="163" ht="20.1" customHeight="1" spans="3:9">
+    <row r="163" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C163" s="13">
         <v>32002</v>
       </c>
@@ -6711,7 +6130,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="164" ht="20.1" customHeight="1" spans="3:9">
+    <row r="164" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C164" s="13">
         <v>32003</v>
       </c>
@@ -6732,7 +6151,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="165" ht="20.1" customHeight="1" spans="3:9">
+    <row r="165" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C165" s="13">
         <v>32004</v>
       </c>
@@ -6753,7 +6172,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="166" ht="20.1" customHeight="1" spans="3:9">
+    <row r="166" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C166" s="13">
         <v>32005</v>
       </c>
@@ -6774,7 +6193,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="167" ht="20.1" customHeight="1" spans="3:9">
+    <row r="167" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C167" s="13">
         <v>32006</v>
       </c>
@@ -6795,7 +6214,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="168" ht="20.1" customHeight="1" spans="3:9">
+    <row r="168" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C168" s="13">
         <v>32007</v>
       </c>
@@ -6816,7 +6235,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="169" ht="20.1" customHeight="1" spans="3:9">
+    <row r="169" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C169" s="13">
         <v>32008</v>
       </c>
@@ -6837,7 +6256,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="170" ht="20.1" customHeight="1" spans="3:9">
+    <row r="170" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C170" s="13">
         <v>33001</v>
       </c>
@@ -6854,7 +6273,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="171" ht="20.1" customHeight="1" spans="3:9">
+    <row r="171" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C171" s="13">
         <v>33002</v>
       </c>
@@ -6871,7 +6290,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="172" ht="20.1" customHeight="1" spans="3:9">
+    <row r="172" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C172" s="13">
         <v>33003</v>
       </c>
@@ -6888,7 +6307,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="173" ht="20.1" customHeight="1" spans="3:9">
+    <row r="173" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C173" s="13">
         <v>33004</v>
       </c>
@@ -6905,7 +6324,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="174" ht="20.1" customHeight="1" spans="3:9">
+    <row r="174" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C174" s="13">
         <v>33005</v>
       </c>
@@ -6922,7 +6341,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="175" ht="20.1" customHeight="1" spans="3:9">
+    <row r="175" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C175" s="13">
         <v>33006</v>
       </c>
@@ -6939,7 +6358,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="176" ht="20.1" customHeight="1" spans="3:9">
+    <row r="176" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C176" s="13">
         <v>33007</v>
       </c>
@@ -6956,7 +6375,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="177" ht="20.1" customHeight="1" spans="3:9">
+    <row r="177" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C177" s="13">
         <v>33008</v>
       </c>
@@ -6973,7 +6392,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="178" ht="20.1" customHeight="1" spans="3:9">
+    <row r="178" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C178" s="13">
         <v>33009</v>
       </c>
@@ -6990,7 +6409,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="179" ht="20.1" customHeight="1" spans="3:9">
+    <row r="179" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C179" s="13">
         <v>33010</v>
       </c>
@@ -7007,7 +6426,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="180" ht="20.1" customHeight="1" spans="3:9">
+    <row r="180" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C180" s="13">
         <v>33011</v>
       </c>
@@ -7024,7 +6443,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="181" ht="20.1" customHeight="1" spans="3:9">
+    <row r="181" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C181" s="13">
         <v>33012</v>
       </c>
@@ -7041,7 +6460,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="182" ht="20.1" customHeight="1" spans="3:9">
+    <row r="182" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C182" s="13">
         <v>33013</v>
       </c>
@@ -7058,7 +6477,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="183" ht="20.1" customHeight="1" spans="3:9">
+    <row r="183" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C183" s="13">
         <v>33014</v>
       </c>
@@ -7075,7 +6494,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="184" ht="20.1" customHeight="1" spans="3:9">
+    <row r="184" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C184" s="13">
         <v>33015</v>
       </c>
@@ -7092,7 +6511,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="185" ht="20.1" customHeight="1" spans="3:9">
+    <row r="185" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C185" s="13">
         <v>33016</v>
       </c>
@@ -7109,7 +6528,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="186" ht="20.1" customHeight="1" spans="3:9">
+    <row r="186" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C186" s="13">
         <v>33017</v>
       </c>
@@ -7126,7 +6545,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="187" ht="20.1" customHeight="1" spans="3:9">
+    <row r="187" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C187" s="13">
         <v>33018</v>
       </c>
@@ -7143,7 +6562,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="188" ht="20.1" customHeight="1" spans="3:9">
+    <row r="188" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C188" s="13">
         <v>33019</v>
       </c>
@@ -7160,7 +6579,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="189" ht="20.1" customHeight="1" spans="3:9">
+    <row r="189" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C189" s="13">
         <v>33020</v>
       </c>
@@ -7177,7 +6596,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="190" ht="20.1" customHeight="1" spans="3:9">
+    <row r="190" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C190" s="13">
         <v>34001</v>
       </c>
@@ -7198,7 +6617,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="191" ht="20.1" customHeight="1" spans="3:9">
+    <row r="191" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C191" s="13">
         <v>34002</v>
       </c>
@@ -7219,7 +6638,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="192" ht="20.1" customHeight="1" spans="3:9">
+    <row r="192" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C192" s="13">
         <v>35001</v>
       </c>
@@ -7236,7 +6655,7 @@
       <c r="H192" s="14"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" ht="20.1" customHeight="1" spans="3:9">
+    <row r="193" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C193" s="13">
         <v>35002</v>
       </c>
@@ -7253,7 +6672,7 @@
       <c r="H193" s="14"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="194" ht="20.1" customHeight="1" spans="3:9">
+    <row r="194" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C194" s="13">
         <v>35003</v>
       </c>
@@ -7270,7 +6689,7 @@
       <c r="H194" s="14"/>
       <c r="I194" s="11"/>
     </row>
-    <row r="195" ht="20.1" customHeight="1" spans="3:9">
+    <row r="195" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C195" s="13">
         <v>35004</v>
       </c>
@@ -7287,7 +6706,7 @@
       <c r="H195" s="14"/>
       <c r="I195" s="11"/>
     </row>
-    <row r="196" ht="20.1" customHeight="1" spans="3:9">
+    <row r="196" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C196" s="13">
         <v>35005</v>
       </c>
@@ -7304,7 +6723,7 @@
       <c r="H196" s="14"/>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" ht="20.1" customHeight="1" spans="3:9">
+    <row r="197" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C197" s="13">
         <v>35006</v>
       </c>
@@ -7321,7 +6740,7 @@
       <c r="H197" s="14"/>
       <c r="I197" s="11"/>
     </row>
-    <row r="198" ht="20.1" customHeight="1" spans="3:9">
+    <row r="198" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C198" s="13">
         <v>35007</v>
       </c>
@@ -7338,7 +6757,7 @@
       <c r="H198" s="14"/>
       <c r="I198" s="11"/>
     </row>
-    <row r="199" ht="20.1" customHeight="1" spans="3:9">
+    <row r="199" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C199" s="13">
         <v>35008</v>
       </c>
@@ -7355,26 +6774,26 @@
       <c r="H199" s="14"/>
       <c r="I199" s="11"/>
     </row>
-    <row r="200" ht="20.1" customHeight="1"/>
-    <row r="201" ht="20.1" customHeight="1"/>
-    <row r="202" ht="20.1" customHeight="1"/>
-    <row r="203" ht="20.1" customHeight="1"/>
-    <row r="204" ht="20.1" customHeight="1"/>
-    <row r="205" ht="20.1" customHeight="1"/>
-    <row r="206" ht="20.1" customHeight="1"/>
-    <row r="207" ht="20.1" customHeight="1"/>
-    <row r="208" ht="20.1" customHeight="1"/>
-    <row r="209" ht="20.1" customHeight="1"/>
-    <row r="210" ht="20.1" customHeight="1"/>
-    <row r="211" ht="20.1" customHeight="1"/>
-    <row r="212" ht="20.1" customHeight="1"/>
+    <row r="200" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>